--- a/3_PROJECT_DATA/prices.xlsx
+++ b/3_PROJECT_DATA/prices.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -466,13 +466,13 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1.431</v>
+        <v>1.419</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -560,13 +560,13 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -607,13 +607,13 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1.431</v>
+        <v>1.419</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -654,13 +654,13 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1.666</v>
+        <v>1.707</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -706,13 +706,13 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1.441</v>
+        <v>1.429</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -758,13 +758,13 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1.666</v>
+        <v>1.707</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -805,13 +805,13 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1.441</v>
+        <v>1.429</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -852,13 +852,13 @@
         <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1.676</v>
+        <v>1.717</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -899,13 +899,13 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -956,13 +956,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1.431</v>
+        <v>1.419</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1013,13 +1013,13 @@
         <v>0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1060,13 +1060,13 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1.441</v>
+        <v>1.429</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1107,13 +1107,13 @@
         <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1154,13 +1154,13 @@
         <v>0</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1.441</v>
+        <v>1.429</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1201,13 +1201,13 @@
         <v>0</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1248,13 +1248,13 @@
         <v>0</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1.441</v>
+        <v>1.429</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1295,13 +1295,13 @@
         <v>0</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1399,13 +1399,13 @@
         <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>1.431</v>
+        <v>1.419</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1451,13 +1451,13 @@
         <v>0</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>1.726</v>
+        <v>1.706</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1503,13 +1503,13 @@
         <v>0</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1607,13 +1607,13 @@
         <v>0</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>1.431</v>
+        <v>1.419</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         <v>0</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>1.726</v>
+        <v>1.706</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1711,13 +1711,13 @@
         <v>0</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1758,13 +1758,13 @@
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>1.441</v>
+        <v>1.429</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1805,13 +1805,13 @@
         <v>0</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1857,13 +1857,13 @@
         <v>0</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>1.421</v>
+        <v>1.409</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1909,13 +1909,13 @@
         <v>0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1956,13 +1956,13 @@
         <v>0</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>1.431</v>
+        <v>1.419</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -2003,13 +2003,13 @@
         <v>0</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2050,13 +2050,13 @@
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2102,13 +2102,13 @@
         <v>0</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>1.431</v>
+        <v>1.419</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2154,13 +2154,13 @@
         <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2201,13 +2201,13 @@
         <v>0</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>1.431</v>
+        <v>1.419</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2295,13 +2295,13 @@
         <v>0</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2399,13 +2399,13 @@
         <v>0</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>1.431</v>
+        <v>1.419</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2451,13 +2451,13 @@
         <v>0</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G42" s="3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>1.726</v>
+        <v>1.706</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2503,13 +2503,13 @@
         <v>0</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2550,13 +2550,13 @@
         <v>0</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>1.431</v>
+        <v>1.419</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2597,13 +2597,13 @@
         <v>0</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2701,13 +2701,13 @@
         <v>0</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G47" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>1.431</v>
+        <v>1.419</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2753,13 +2753,13 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>1.726</v>
+        <v>1.706</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2805,13 +2805,13 @@
         <v>0</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G49" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2909,13 +2909,13 @@
         <v>0</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G51" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>1.431</v>
+        <v>1.419</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G52" s="3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>1.726</v>
+        <v>1.706</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -3013,13 +3013,13 @@
         <v>0</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G53" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -3050,13 +3050,13 @@
         <v>0</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G54" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>1.666</v>
+        <v>1.707</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -3087,13 +3087,13 @@
         <v>0</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G55" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -3124,13 +3124,13 @@
         <v>0</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G56" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -3161,13 +3161,13 @@
         <v>0</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G57" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -3198,13 +3198,13 @@
         <v>0</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G58" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>1.441</v>
+        <v>1.429</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -3235,13 +3235,13 @@
         <v>0</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G59" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>1.431</v>
+        <v>1.419</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -3272,13 +3272,13 @@
         <v>0</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G60" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>1.666</v>
+        <v>1.707</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -3309,13 +3309,13 @@
         <v>0</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G61" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>1.441</v>
+        <v>1.429</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -3346,13 +3346,13 @@
         <v>0</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G62" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>1.421</v>
+        <v>1.409</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -3383,13 +3383,13 @@
         <v>0</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G63" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>1.421</v>
+        <v>1.409</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -3420,13 +3420,13 @@
         <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>1.441</v>
+        <v>1.429</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -3457,13 +3457,13 @@
         <v>0</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G65" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -3504,13 +3504,13 @@
         <v>0</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G66" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>1.421</v>
+        <v>1.409</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -3551,13 +3551,13 @@
         <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -3588,13 +3588,13 @@
         <v>0</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G68" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>1.431</v>
+        <v>1.419</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -3625,13 +3625,13 @@
         <v>0</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G69" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="B70" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -3699,13 +3699,13 @@
         <v>0</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G71" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         </is>
       </c>
       <c r="B72" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -3736,13 +3736,13 @@
         <v>0</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G72" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="B73" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -3773,13 +3773,13 @@
         <v>0</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G73" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="B74" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="B75" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -3847,13 +3847,13 @@
         <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G75" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="B76" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -3884,13 +3884,13 @@
         <v>0</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G76" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="B77" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3921,13 +3921,13 @@
         <v>0</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G77" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         </is>
       </c>
       <c r="B78" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3973,13 +3973,13 @@
         <v>0</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G78" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>1.421</v>
+        <v>1.409</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -4025,13 +4025,13 @@
         <v>0</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G79" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>1.666</v>
+        <v>1.707</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -4072,13 +4072,13 @@
         <v>0</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G80" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>1.441</v>
+        <v>1.429</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -4119,13 +4119,13 @@
         <v>0.04</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G81" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0.04</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G82" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="B83" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -4193,13 +4193,13 @@
         <v>0.04</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G83" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="B84" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -4230,13 +4230,13 @@
         <v>0</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G84" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="B85" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="B86" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -4304,13 +4304,13 @@
         <v>0</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G86" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="B87" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -4341,13 +4341,13 @@
         <v>0</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G87" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         </is>
       </c>
       <c r="B88" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="B89" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -4415,13 +4415,13 @@
         <v>0.04</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G89" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         </is>
       </c>
       <c r="B90" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -4452,13 +4452,13 @@
         <v>0.05</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G90" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -4489,13 +4489,13 @@
         <v>0</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G91" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>1.656</v>
+        <v>1.697</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -4526,13 +4526,13 @@
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>1.431</v>
+        <v>1.419</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -4563,13 +4563,13 @@
         <v>0.03</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G93" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         </is>
       </c>
       <c r="B95" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -4637,13 +4637,13 @@
         <v>0.03</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G95" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N95" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         </is>
       </c>
       <c r="B96" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -4674,13 +4674,13 @@
         <v>0.04</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G96" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="B97" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="B98" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -4748,13 +4748,13 @@
         <v>0.03</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G98" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="B99" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="B100" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -4822,13 +4822,13 @@
         <v>0.03</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="B101" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -4859,13 +4859,13 @@
         <v>0.04</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G101" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="B102" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         </is>
       </c>
       <c r="B103" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -4933,13 +4933,13 @@
         <v>0.03</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G103" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N103" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         </is>
       </c>
       <c r="B104" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="B105" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -5007,13 +5007,13 @@
         <v>0.03</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G105" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N105" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="B106" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -5044,13 +5044,13 @@
         <v>0.04</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G106" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N106" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -5118,13 +5118,13 @@
         <v>0.03</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G108" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N108" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -5192,13 +5192,13 @@
         <v>0.03</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G110" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N110" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="B111" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -5229,13 +5229,13 @@
         <v>0.04</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N111" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         </is>
       </c>
       <c r="B112" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         </is>
       </c>
       <c r="B113" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -5303,13 +5303,13 @@
         <v>0.03</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G113" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N113" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         </is>
       </c>
       <c r="B114" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         </is>
       </c>
       <c r="B115" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -5377,13 +5377,13 @@
         <v>0.03</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N115" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="B116" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -5414,13 +5414,13 @@
         <v>0.04</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G116" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N116" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="B117" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="B118" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -5488,13 +5488,13 @@
         <v>0.03</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N118" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="B119" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="B120" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -5562,13 +5562,13 @@
         <v>0.03</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G120" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N120" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="B121" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -5599,13 +5599,13 @@
         <v>0.04</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G121" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N121" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="B122" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         </is>
       </c>
       <c r="B123" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -5673,13 +5673,13 @@
         <v>0.03</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G123" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N123" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         </is>
       </c>
       <c r="B124" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="B125" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -5747,13 +5747,13 @@
         <v>0.03</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G125" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N125" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         </is>
       </c>
       <c r="B126" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
         <v>0.04</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G126" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N126" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="B127" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         </is>
       </c>
       <c r="B128" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -5858,13 +5858,13 @@
         <v>0.03</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G128" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N128" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         </is>
       </c>
       <c r="B129" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -5895,13 +5895,13 @@
         <v>0.03</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G129" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N129" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         </is>
       </c>
       <c r="B130" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="B131" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -5969,13 +5969,13 @@
         <v>0.04</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G131" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N131" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="B132" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="B133" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -6043,13 +6043,13 @@
         <v>0.03</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G133" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N133" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         </is>
       </c>
       <c r="B134" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="B135" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0.03</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N135" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         </is>
       </c>
       <c r="B136" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -6154,13 +6154,13 @@
         <v>0.04</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G136" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N136" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="B137" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="B138" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -6228,13 +6228,13 @@
         <v>0.03</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G138" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N138" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         </is>
       </c>
       <c r="B139" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         </is>
       </c>
       <c r="B140" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -6302,13 +6302,13 @@
         <v>0.03</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G140" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N140" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         </is>
       </c>
       <c r="B141" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -6339,13 +6339,13 @@
         <v>0.04</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G141" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N141" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         </is>
       </c>
       <c r="B142" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="B143" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -6413,13 +6413,13 @@
         <v>0.03</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G143" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N143" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         </is>
       </c>
       <c r="B144" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="B145" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -6487,13 +6487,13 @@
         <v>0.03</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G145" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N145" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         </is>
       </c>
       <c r="B146" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -6524,13 +6524,13 @@
         <v>0.04</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G146" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N146" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="B147" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         </is>
       </c>
       <c r="B148" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -6598,13 +6598,13 @@
         <v>0.03</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G148" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N148" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="B149" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="B150" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -6672,13 +6672,13 @@
         <v>0.03</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G150" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N150" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="B151" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -6709,13 +6709,13 @@
         <v>0.04</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G151" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N151" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="B152" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         </is>
       </c>
       <c r="B153" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -6783,13 +6783,13 @@
         <v>0.03</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G153" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N153" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         </is>
       </c>
       <c r="B154" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         </is>
       </c>
       <c r="B155" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -6857,13 +6857,13 @@
         <v>0.03</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G155" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N155" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="B156" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -6894,13 +6894,13 @@
         <v>0.04</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G156" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N156" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="B157" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="B158" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -6968,13 +6968,13 @@
         <v>0.03</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G158" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N158" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="B159" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="B160" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -7042,13 +7042,13 @@
         <v>0.03</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G160" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N160" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         </is>
       </c>
       <c r="B161" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -7079,13 +7079,13 @@
         <v>0.04</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G161" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N161" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="B162" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="B163" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -7153,13 +7153,13 @@
         <v>0.03</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G163" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N163" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         </is>
       </c>
       <c r="B164" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="B165" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -7227,13 +7227,13 @@
         <v>0.03</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G165" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N165" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         </is>
       </c>
       <c r="B166" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -7264,13 +7264,13 @@
         <v>0.04</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G166" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N166" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         </is>
       </c>
       <c r="B167" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         </is>
       </c>
       <c r="B168" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -7338,13 +7338,13 @@
         <v>0.03</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G168" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N168" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         </is>
       </c>
       <c r="B169" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         </is>
       </c>
       <c r="B170" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -7412,13 +7412,13 @@
         <v>0.03</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G170" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N170" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="B171" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -7449,13 +7449,13 @@
         <v>0.04</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G171" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N171" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="B172" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="B173" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -7523,13 +7523,13 @@
         <v>0.03</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G173" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N173" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         </is>
       </c>
       <c r="B174" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         </is>
       </c>
       <c r="B175" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -7597,13 +7597,13 @@
         <v>0.03</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G175" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N175" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="B176" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -7634,13 +7634,13 @@
         <v>0.04</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G176" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N176" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="B177" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         </is>
       </c>
       <c r="B178" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -7708,13 +7708,13 @@
         <v>0.03</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G178" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N178" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         </is>
       </c>
       <c r="B179" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         </is>
       </c>
       <c r="B180" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -7782,13 +7782,13 @@
         <v>0.03</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G180" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N180" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="B181" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -7819,13 +7819,13 @@
         <v>0.04</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G181" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N181" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         </is>
       </c>
       <c r="B182" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="B183" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -7893,13 +7893,13 @@
         <v>0.03</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G183" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N183" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         </is>
       </c>
       <c r="B184" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         </is>
       </c>
       <c r="B185" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -7967,13 +7967,13 @@
         <v>0.03</v>
       </c>
       <c r="F185" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G185" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N185" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         </is>
       </c>
       <c r="B186" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -8004,13 +8004,13 @@
         <v>0.04</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G186" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N186" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         </is>
       </c>
       <c r="B187" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         </is>
       </c>
       <c r="B188" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -8078,13 +8078,13 @@
         <v>0.03</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G188" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N188" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         </is>
       </c>
       <c r="B189" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -8115,13 +8115,13 @@
         <v>0.03</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G189" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N189" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="B190" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="B191" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -8189,13 +8189,13 @@
         <v>0.04</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G191" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N191" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         </is>
       </c>
       <c r="B192" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         </is>
       </c>
       <c r="B193" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -8263,13 +8263,13 @@
         <v>0.03</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G193" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N193" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         </is>
       </c>
       <c r="B194" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         </is>
       </c>
       <c r="B195" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -8337,13 +8337,13 @@
         <v>0.03</v>
       </c>
       <c r="F195" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G195" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N195" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         </is>
       </c>
       <c r="B196" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -8374,13 +8374,13 @@
         <v>0.04</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G196" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N196" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="B197" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="B198" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -8448,13 +8448,13 @@
         <v>0.03</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G198" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N198" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         </is>
       </c>
       <c r="B199" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         </is>
       </c>
       <c r="B200" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -8522,13 +8522,13 @@
         <v>0.03</v>
       </c>
       <c r="F200" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G200" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N200" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="B201" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -8559,13 +8559,13 @@
         <v>0.04</v>
       </c>
       <c r="F201" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G201" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N201" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         </is>
       </c>
       <c r="B202" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="B203" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -8633,13 +8633,13 @@
         <v>0.03</v>
       </c>
       <c r="F203" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G203" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N203" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="B204" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         </is>
       </c>
       <c r="B205" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -8707,13 +8707,13 @@
         <v>0.03</v>
       </c>
       <c r="F205" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G205" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N205" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="B206" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -8744,13 +8744,13 @@
         <v>0.04</v>
       </c>
       <c r="F206" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G206" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N206" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="B207" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         </is>
       </c>
       <c r="B208" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -8818,13 +8818,13 @@
         <v>0.03</v>
       </c>
       <c r="F208" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G208" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N208" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         </is>
       </c>
       <c r="B209" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         </is>
       </c>
       <c r="B210" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -8892,13 +8892,13 @@
         <v>0.03</v>
       </c>
       <c r="F210" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G210" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N210" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         </is>
       </c>
       <c r="B211" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -8929,13 +8929,13 @@
         <v>0.04</v>
       </c>
       <c r="F211" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G211" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N211" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="B212" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="B213" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -9003,13 +9003,13 @@
         <v>0.03</v>
       </c>
       <c r="F213" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G213" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N213" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         </is>
       </c>
       <c r="B214" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         </is>
       </c>
       <c r="B215" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -9077,13 +9077,13 @@
         <v>0.03</v>
       </c>
       <c r="F215" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G215" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N215" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         </is>
       </c>
       <c r="B216" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -9114,13 +9114,13 @@
         <v>0.04</v>
       </c>
       <c r="F216" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G216" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N216" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         </is>
       </c>
       <c r="B217" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="B218" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -9188,13 +9188,13 @@
         <v>0.03</v>
       </c>
       <c r="F218" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G218" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N218" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         </is>
       </c>
       <c r="B219" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="B220" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -9262,13 +9262,13 @@
         <v>0.03</v>
       </c>
       <c r="F220" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G220" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N220" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="B221" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -9299,13 +9299,13 @@
         <v>0.04</v>
       </c>
       <c r="F221" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G221" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N221" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         </is>
       </c>
       <c r="B222" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="B223" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -9373,13 +9373,13 @@
         <v>0.03</v>
       </c>
       <c r="F223" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G223" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H223" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N223" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="B224" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="B225" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -9447,13 +9447,13 @@
         <v>0.03</v>
       </c>
       <c r="F225" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G225" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H225" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N225" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         </is>
       </c>
       <c r="B226" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -9484,13 +9484,13 @@
         <v>0.04</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G226" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H226" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N226" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         </is>
       </c>
       <c r="B227" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         </is>
       </c>
       <c r="B228" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -9558,13 +9558,13 @@
         <v>0.03</v>
       </c>
       <c r="F228" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G228" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H228" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N228" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="B229" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         </is>
       </c>
       <c r="B230" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -9632,13 +9632,13 @@
         <v>0.03</v>
       </c>
       <c r="F230" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G230" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H230" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N230" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         </is>
       </c>
       <c r="B231" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -9669,13 +9669,13 @@
         <v>0.04</v>
       </c>
       <c r="F231" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G231" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H231" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N231" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         </is>
       </c>
       <c r="B232" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="B233" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -9743,13 +9743,13 @@
         <v>0.03</v>
       </c>
       <c r="F233" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G233" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H233" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N233" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         </is>
       </c>
       <c r="B234" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         </is>
       </c>
       <c r="B235" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -9817,13 +9817,13 @@
         <v>0.03</v>
       </c>
       <c r="F235" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G235" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H235" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N235" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         </is>
       </c>
       <c r="B236" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -9854,13 +9854,13 @@
         <v>0.04</v>
       </c>
       <c r="F236" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G236" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H236" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N236" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="B237" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         </is>
       </c>
       <c r="B238" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -9928,13 +9928,13 @@
         <v>0.03</v>
       </c>
       <c r="F238" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G238" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H238" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N238" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="B239" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -9965,13 +9965,13 @@
         <v>0.03</v>
       </c>
       <c r="F239" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G239" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H239" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N239" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         </is>
       </c>
       <c r="B240" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         </is>
       </c>
       <c r="B241" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -10039,13 +10039,13 @@
         <v>0.04</v>
       </c>
       <c r="F241" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G241" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H241" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N241" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         </is>
       </c>
       <c r="B242" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         </is>
       </c>
       <c r="B243" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -10113,13 +10113,13 @@
         <v>0.03</v>
       </c>
       <c r="F243" s="3" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="G243" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H243" s="2" t="n">
-        <v>1.636</v>
+        <v>1.677</v>
       </c>
       <c r="N243" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         </is>
       </c>
       <c r="B244" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="B245" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -10187,13 +10187,13 @@
         <v>0.03</v>
       </c>
       <c r="F245" s="3" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="G245" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H245" s="2" t="n">
-        <v>1.401</v>
+        <v>1.389</v>
       </c>
       <c r="N245" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         </is>
       </c>
       <c r="B246" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -10224,13 +10224,13 @@
         <v>0.04</v>
       </c>
       <c r="F246" s="3" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="G246" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H246" s="2" t="n">
-        <v>1.656</v>
+        <v>1.636</v>
       </c>
       <c r="N246" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         </is>
       </c>
       <c r="B247" s="1" t="n">
-        <v>46143</v>
+        <v>46136</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -10272,154 +10272,6 @@
       <c r="N247" t="inlineStr">
         <is>
           <t>0000934420042</t>
-        </is>
-      </c>
-    </row>
-    <row r="248" ht="19.2" customHeight="1">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>0386</t>
-        </is>
-      </c>
-      <c r="B248" s="1" t="n">
-        <v>46143</v>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>ДИМИТРОВ ЕКСПРЕС КАРГО ООД</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>Diesel EKONOMY</t>
-        </is>
-      </c>
-      <c r="E248" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F248" s="3" t="n">
-        <v>1.636</v>
-      </c>
-      <c r="G248" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H248" s="2" t="n">
-        <v>1.636</v>
-      </c>
-      <c r="N248" t="inlineStr">
-        <is>
-          <t>148142697</t>
-        </is>
-      </c>
-    </row>
-    <row r="249" ht="19.2" customHeight="1">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>0387</t>
-        </is>
-      </c>
-      <c r="B249" s="1" t="n">
-        <v>46143</v>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>ДИМИТРОВ ЕКСПРЕС КАРГО ООД</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>Diesel Double Filtered</t>
-        </is>
-      </c>
-      <c r="E249" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F249" s="3" t="n">
-        <v>1.776</v>
-      </c>
-      <c r="G249" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H249" s="2" t="n">
-        <v>1.776</v>
-      </c>
-      <c r="N249" t="inlineStr">
-        <is>
-          <t>148142697</t>
-        </is>
-      </c>
-    </row>
-    <row r="250" ht="19.2" customHeight="1">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>0388</t>
-        </is>
-      </c>
-      <c r="B250" s="1" t="n">
-        <v>46143</v>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>ДИМИТРОВ ЕКСПРЕС КАРГО ООД</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>95 EKONOMY Unleaded</t>
-        </is>
-      </c>
-      <c r="E250" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F250" s="3" t="n">
-        <v>1.401</v>
-      </c>
-      <c r="G250" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H250" s="2" t="n">
-        <v>1.401</v>
-      </c>
-      <c r="N250" t="inlineStr">
-        <is>
-          <t>148142697</t>
-        </is>
-      </c>
-    </row>
-    <row r="251" ht="19.2" customHeight="1">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>0389</t>
-        </is>
-      </c>
-      <c r="B251" s="1" t="n">
-        <v>46143</v>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>ДИМИТРОВ ЕКСПРЕС КАРГО ООД</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>EKO Racing 100</t>
-        </is>
-      </c>
-      <c r="E251" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F251" s="3" t="n">
-        <v>1.656</v>
-      </c>
-      <c r="G251" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H251" s="2" t="n">
-        <v>1.656</v>
-      </c>
-      <c r="N251" t="inlineStr">
-        <is>
-          <t>148142697</t>
         </is>
       </c>
     </row>

--- a/3_PROJECT_DATA/prices.xlsx
+++ b/3_PROJECT_DATA/prices.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -466,13 +466,13 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1.697</v>
+        <v>1.666</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -560,13 +560,13 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1.697</v>
+        <v>1.666</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -654,13 +654,13 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1.707</v>
+        <v>1.676</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -758,13 +758,13 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1.707</v>
+        <v>1.676</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -852,13 +852,13 @@
         <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1.717</v>
+        <v>1.686</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -899,13 +899,13 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1.697</v>
+        <v>1.666</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1013,13 +1013,13 @@
         <v>0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1.697</v>
+        <v>1.666</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1107,13 +1107,13 @@
         <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1.697</v>
+        <v>1.666</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1201,13 +1201,13 @@
         <v>0</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1.697</v>
+        <v>1.666</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1295,13 +1295,13 @@
         <v>0</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1.697</v>
+        <v>1.666</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1503,13 +1503,13 @@
         <v>0</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>1.697</v>
+        <v>1.666</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1711,13 +1711,13 @@
         <v>0</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>1.697</v>
+        <v>1.666</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1805,13 +1805,13 @@
         <v>0</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>1.697</v>
+        <v>1.666</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1909,13 +1909,13 @@
         <v>0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>1.697</v>
+        <v>1.666</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -2003,13 +2003,13 @@
         <v>0</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>1.697</v>
+        <v>1.666</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2050,13 +2050,13 @@
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>1.697</v>
+        <v>1.666</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2154,13 +2154,13 @@
         <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>1.697</v>
+        <v>1.666</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2201,13 +2201,13 @@
         <v>0</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>1.697</v>
+        <v>1.666</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2295,13 +2295,13 @@
         <v>0</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>1.697</v>
+        <v>1.666</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2503,13 +2503,13 @@
         <v>0</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>1.697</v>
+        <v>1.666</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2597,13 +2597,13 @@
         <v>0</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>1.697</v>
+        <v>1.666</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2805,13 +2805,13 @@
         <v>0</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G49" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>1.697</v>
+        <v>1.666</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -3013,13 +3013,13 @@
         <v>0</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G53" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>1.697</v>
+        <v>1.666</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -3050,13 +3050,13 @@
         <v>0</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G54" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>1.707</v>
+        <v>1.676</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -3087,13 +3087,13 @@
         <v>0</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G55" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>1.697</v>
+        <v>1.666</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -3124,13 +3124,13 @@
         <v>0</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G56" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>1.697</v>
+        <v>1.666</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -3161,13 +3161,13 @@
         <v>0</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G57" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>1.697</v>
+        <v>1.666</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -3272,13 +3272,13 @@
         <v>0</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G60" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>1.707</v>
+        <v>1.676</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -3457,13 +3457,13 @@
         <v>0</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G65" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>1.697</v>
+        <v>1.666</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -3551,13 +3551,13 @@
         <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>1.697</v>
+        <v>1.666</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -3625,13 +3625,13 @@
         <v>0</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G69" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="B70" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         </is>
       </c>
       <c r="B72" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="B73" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -3773,13 +3773,13 @@
         <v>0</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G73" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="B74" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="B75" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="B76" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="B77" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3921,13 +3921,13 @@
         <v>0</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G77" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>1.697</v>
+        <v>1.666</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         </is>
       </c>
       <c r="B78" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -4025,13 +4025,13 @@
         <v>0</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G79" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>1.707</v>
+        <v>1.676</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -4119,13 +4119,13 @@
         <v>0.04</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G81" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="B83" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -4193,13 +4193,13 @@
         <v>0.04</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G83" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="B84" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -4230,13 +4230,13 @@
         <v>0</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G84" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="B85" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="B86" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="B87" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         </is>
       </c>
       <c r="B88" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="B89" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         </is>
       </c>
       <c r="B90" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -4489,13 +4489,13 @@
         <v>0</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G91" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>1.697</v>
+        <v>1.666</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -4563,13 +4563,13 @@
         <v>0.03</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G93" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         </is>
       </c>
       <c r="B95" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         </is>
       </c>
       <c r="B96" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="B97" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="B98" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -4748,13 +4748,13 @@
         <v>0.03</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G98" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="B99" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="B100" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="B101" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="B102" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         </is>
       </c>
       <c r="B103" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -4933,13 +4933,13 @@
         <v>0.03</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G103" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N103" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         </is>
       </c>
       <c r="B104" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="B105" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="B106" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -5118,13 +5118,13 @@
         <v>0.03</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G108" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N108" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="B111" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         </is>
       </c>
       <c r="B112" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         </is>
       </c>
       <c r="B113" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -5303,13 +5303,13 @@
         <v>0.03</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G113" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N113" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         </is>
       </c>
       <c r="B114" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         </is>
       </c>
       <c r="B115" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="B116" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="B117" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="B118" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -5488,13 +5488,13 @@
         <v>0.03</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N118" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="B119" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="B120" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="B121" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="B122" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         </is>
       </c>
       <c r="B123" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -5673,13 +5673,13 @@
         <v>0.03</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G123" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N123" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         </is>
       </c>
       <c r="B124" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="B125" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         </is>
       </c>
       <c r="B126" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="B127" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         </is>
       </c>
       <c r="B128" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -5858,13 +5858,13 @@
         <v>0.03</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G128" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N128" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         </is>
       </c>
       <c r="B129" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         </is>
       </c>
       <c r="B130" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="B131" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="B132" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="B133" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -6043,13 +6043,13 @@
         <v>0.03</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G133" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N133" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         </is>
       </c>
       <c r="B134" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="B135" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         </is>
       </c>
       <c r="B136" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="B137" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="B138" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -6228,13 +6228,13 @@
         <v>0.03</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G138" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N138" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         </is>
       </c>
       <c r="B139" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         </is>
       </c>
       <c r="B140" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         </is>
       </c>
       <c r="B141" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         </is>
       </c>
       <c r="B142" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="B143" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -6413,13 +6413,13 @@
         <v>0.03</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G143" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N143" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         </is>
       </c>
       <c r="B144" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="B145" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         </is>
       </c>
       <c r="B146" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="B147" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         </is>
       </c>
       <c r="B148" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -6598,13 +6598,13 @@
         <v>0.03</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G148" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N148" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="B149" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="B150" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="B151" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="B152" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         </is>
       </c>
       <c r="B153" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -6783,13 +6783,13 @@
         <v>0.03</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G153" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N153" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         </is>
       </c>
       <c r="B154" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         </is>
       </c>
       <c r="B155" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="B156" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="B157" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="B158" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -6968,13 +6968,13 @@
         <v>0.03</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G158" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N158" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="B159" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="B160" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         </is>
       </c>
       <c r="B161" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="B162" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="B163" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -7153,13 +7153,13 @@
         <v>0.03</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G163" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N163" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         </is>
       </c>
       <c r="B164" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="B165" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         </is>
       </c>
       <c r="B166" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         </is>
       </c>
       <c r="B167" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         </is>
       </c>
       <c r="B168" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -7338,13 +7338,13 @@
         <v>0.03</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G168" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N168" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         </is>
       </c>
       <c r="B169" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         </is>
       </c>
       <c r="B170" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="B171" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="B172" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="B173" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -7523,13 +7523,13 @@
         <v>0.03</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G173" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N173" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         </is>
       </c>
       <c r="B174" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         </is>
       </c>
       <c r="B175" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="B176" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="B177" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         </is>
       </c>
       <c r="B178" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -7708,13 +7708,13 @@
         <v>0.03</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G178" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N178" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         </is>
       </c>
       <c r="B179" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         </is>
       </c>
       <c r="B180" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="B181" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         </is>
       </c>
       <c r="B182" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="B183" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -7893,13 +7893,13 @@
         <v>0.03</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G183" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N183" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         </is>
       </c>
       <c r="B184" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         </is>
       </c>
       <c r="B185" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         </is>
       </c>
       <c r="B186" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         </is>
       </c>
       <c r="B187" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         </is>
       </c>
       <c r="B188" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -8078,13 +8078,13 @@
         <v>0.03</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G188" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N188" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         </is>
       </c>
       <c r="B189" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="B190" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="B191" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         </is>
       </c>
       <c r="B192" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         </is>
       </c>
       <c r="B193" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -8263,13 +8263,13 @@
         <v>0.03</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G193" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N193" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         </is>
       </c>
       <c r="B194" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         </is>
       </c>
       <c r="B195" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         </is>
       </c>
       <c r="B196" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="B197" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="B198" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -8448,13 +8448,13 @@
         <v>0.03</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G198" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N198" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         </is>
       </c>
       <c r="B199" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         </is>
       </c>
       <c r="B200" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="B201" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         </is>
       </c>
       <c r="B202" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="B203" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -8633,13 +8633,13 @@
         <v>0.03</v>
       </c>
       <c r="F203" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G203" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N203" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="B204" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         </is>
       </c>
       <c r="B205" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="B206" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="B207" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         </is>
       </c>
       <c r="B208" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -8818,13 +8818,13 @@
         <v>0.03</v>
       </c>
       <c r="F208" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G208" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N208" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         </is>
       </c>
       <c r="B209" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         </is>
       </c>
       <c r="B210" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         </is>
       </c>
       <c r="B211" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="B212" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="B213" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -9003,13 +9003,13 @@
         <v>0.03</v>
       </c>
       <c r="F213" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G213" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N213" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         </is>
       </c>
       <c r="B214" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         </is>
       </c>
       <c r="B215" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         </is>
       </c>
       <c r="B216" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         </is>
       </c>
       <c r="B217" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="B218" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -9188,13 +9188,13 @@
         <v>0.03</v>
       </c>
       <c r="F218" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G218" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N218" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         </is>
       </c>
       <c r="B219" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="B220" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="B221" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         </is>
       </c>
       <c r="B222" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="B223" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -9373,13 +9373,13 @@
         <v>0.03</v>
       </c>
       <c r="F223" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G223" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H223" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N223" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="B224" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="B225" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         </is>
       </c>
       <c r="B226" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         </is>
       </c>
       <c r="B227" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         </is>
       </c>
       <c r="B228" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -9558,13 +9558,13 @@
         <v>0.03</v>
       </c>
       <c r="F228" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G228" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H228" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N228" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="B229" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         </is>
       </c>
       <c r="B230" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         </is>
       </c>
       <c r="B231" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         </is>
       </c>
       <c r="B232" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="B233" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -9743,13 +9743,13 @@
         <v>0.03</v>
       </c>
       <c r="F233" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G233" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H233" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N233" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         </is>
       </c>
       <c r="B234" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         </is>
       </c>
       <c r="B235" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         </is>
       </c>
       <c r="B236" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="B237" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         </is>
       </c>
       <c r="B238" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -9928,13 +9928,13 @@
         <v>0.03</v>
       </c>
       <c r="F238" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G238" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H238" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N238" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="B239" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         </is>
       </c>
       <c r="B240" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         </is>
       </c>
       <c r="B241" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         </is>
       </c>
       <c r="B242" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         </is>
       </c>
       <c r="B243" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -10113,13 +10113,13 @@
         <v>0.03</v>
       </c>
       <c r="F243" s="3" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="G243" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H243" s="2" t="n">
-        <v>1.677</v>
+        <v>1.646</v>
       </c>
       <c r="N243" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         </is>
       </c>
       <c r="B244" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="B245" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         </is>
       </c>
       <c r="B246" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         </is>
       </c>
       <c r="B247" s="1" t="n">
-        <v>46136</v>
+        <v>46141</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -10272,6 +10272,154 @@
       <c r="N247" t="inlineStr">
         <is>
           <t>0000934420042</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="19.2" customHeight="1">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>0386</t>
+        </is>
+      </c>
+      <c r="B248" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>ДИМИТРОВ ЕКСПРЕС КАРГО ООД</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Diesel EKONOMY</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F248" s="3" t="n">
+        <v>1.646</v>
+      </c>
+      <c r="G248" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" s="2" t="n">
+        <v>1.646</v>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>148142697</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="19.2" customHeight="1">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>0387</t>
+        </is>
+      </c>
+      <c r="B249" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>ДИМИТРОВ ЕКСПРЕС КАРГО ООД</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Diesel Double Filtered</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F249" s="3" t="n">
+        <v>1.776</v>
+      </c>
+      <c r="G249" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" s="2" t="n">
+        <v>1.776</v>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>148142697</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="19.2" customHeight="1">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>0388</t>
+        </is>
+      </c>
+      <c r="B250" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>ДИМИТРОВ ЕКСПРЕС КАРГО ООД</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>95 EKONOMY Unleaded</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F250" s="3" t="n">
+        <v>1.389</v>
+      </c>
+      <c r="G250" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" s="2" t="n">
+        <v>1.389</v>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>148142697</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="19.2" customHeight="1">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>0389</t>
+        </is>
+      </c>
+      <c r="B251" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>ДИМИТРОВ ЕКСПРЕС КАРГО ООД</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>EKO Racing 100</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F251" s="3" t="n">
+        <v>1.636</v>
+      </c>
+      <c r="G251" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H251" s="2" t="n">
+        <v>1.636</v>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>148142697</t>
         </is>
       </c>
     </row>

--- a/3_PROJECT_DATA/prices.xlsx
+++ b/3_PROJECT_DATA/prices.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -466,13 +466,13 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1.629</v>
+        <v>1.619</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1.504</v>
+        <v>1.524</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -560,13 +560,13 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1.629</v>
+        <v>1.619</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -607,13 +607,13 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1.504</v>
+        <v>1.524</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -654,13 +654,13 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0.05</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1.639</v>
+        <v>1.629</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -706,13 +706,13 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1.504</v>
+        <v>1.524</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -758,13 +758,13 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0.05</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1.639</v>
+        <v>1.629</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -805,13 +805,13 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1.504</v>
+        <v>1.524</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -852,13 +852,13 @@
         <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0.06</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1.649</v>
+        <v>1.639</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -899,13 +899,13 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1.629</v>
+        <v>1.619</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -956,13 +956,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1.504</v>
+        <v>1.524</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1013,13 +1013,13 @@
         <v>0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1.629</v>
+        <v>1.619</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1060,13 +1060,13 @@
         <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1.504</v>
+        <v>1.524</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1107,13 +1107,13 @@
         <v>0</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1.629</v>
+        <v>1.619</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1154,13 +1154,13 @@
         <v>0</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1.504</v>
+        <v>1.524</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1201,13 +1201,13 @@
         <v>0</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1.629</v>
+        <v>1.619</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1248,13 +1248,13 @@
         <v>0</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1.504</v>
+        <v>1.524</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1295,13 +1295,13 @@
         <v>0</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1.629</v>
+        <v>1.619</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1399,13 +1399,13 @@
         <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>1.494</v>
+        <v>1.514</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1451,13 +1451,13 @@
         <v>0</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>1.78</v>
+        <v>1.798</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1503,13 +1503,13 @@
         <v>0</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>1.619</v>
+        <v>1.609</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1607,13 +1607,13 @@
         <v>0</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>1.494</v>
+        <v>1.514</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1659,13 +1659,13 @@
         <v>0</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>1.78</v>
+        <v>1.798</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1711,13 +1711,13 @@
         <v>0</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>1.629</v>
+        <v>1.619</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1758,13 +1758,13 @@
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>1.504</v>
+        <v>1.524</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1805,13 +1805,13 @@
         <v>0</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>1.609</v>
+        <v>1.599</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1857,13 +1857,13 @@
         <v>0</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>1.484</v>
+        <v>1.504</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1909,13 +1909,13 @@
         <v>0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>1.629</v>
+        <v>1.619</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1956,13 +1956,13 @@
         <v>0</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>1.504</v>
+        <v>1.524</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -2003,13 +2003,13 @@
         <v>0</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>1.619</v>
+        <v>1.609</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2050,13 +2050,13 @@
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>1.619</v>
+        <v>1.609</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2102,13 +2102,13 @@
         <v>0</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>1.494</v>
+        <v>1.514</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2154,13 +2154,13 @@
         <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>1.609</v>
+        <v>1.599</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2201,13 +2201,13 @@
         <v>0</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>1.629</v>
+        <v>1.619</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>1.494</v>
+        <v>1.514</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2295,13 +2295,13 @@
         <v>0</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>1.629</v>
+        <v>1.619</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2399,13 +2399,13 @@
         <v>0</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>1.494</v>
+        <v>1.514</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2451,13 +2451,13 @@
         <v>0</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G42" s="3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>1.78</v>
+        <v>1.798</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2503,13 +2503,13 @@
         <v>0</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>1.629</v>
+        <v>1.619</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2550,13 +2550,13 @@
         <v>0</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>1.504</v>
+        <v>1.524</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2597,13 +2597,13 @@
         <v>0</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>1.629</v>
+        <v>1.619</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2701,13 +2701,13 @@
         <v>0</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G47" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>1.494</v>
+        <v>1.514</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2753,13 +2753,13 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>1.78</v>
+        <v>1.798</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2805,13 +2805,13 @@
         <v>0</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G49" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>1.629</v>
+        <v>1.619</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2909,13 +2909,13 @@
         <v>0</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G51" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>1.494</v>
+        <v>1.514</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G52" s="3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>1.78</v>
+        <v>1.798</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -3013,13 +3013,13 @@
         <v>0</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G53" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>1.629</v>
+        <v>1.619</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -3050,13 +3050,13 @@
         <v>0</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G54" s="3" t="n">
         <v>0.03</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>1.619</v>
+        <v>1.609</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -3087,13 +3087,13 @@
         <v>0</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G55" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>1.629</v>
+        <v>1.619</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -3124,13 +3124,13 @@
         <v>0</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G56" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>1.609</v>
+        <v>1.599</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -3161,13 +3161,13 @@
         <v>0</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G57" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>1.609</v>
+        <v>1.599</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -3198,13 +3198,13 @@
         <v>0</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G58" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>1.504</v>
+        <v>1.524</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -3235,13 +3235,13 @@
         <v>0</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G59" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>1.504</v>
+        <v>1.524</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -3272,13 +3272,13 @@
         <v>0</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G60" s="3" t="n">
         <v>0.05</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>1.639</v>
+        <v>1.629</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -3309,13 +3309,13 @@
         <v>0</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G61" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>1.504</v>
+        <v>1.524</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -3346,13 +3346,13 @@
         <v>0</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G62" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>1.484</v>
+        <v>1.504</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -3383,13 +3383,13 @@
         <v>0</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G63" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>1.484</v>
+        <v>1.504</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -3420,13 +3420,13 @@
         <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>1.504</v>
+        <v>1.524</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -3457,13 +3457,13 @@
         <v>0</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G65" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>1.609</v>
+        <v>1.599</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -3504,13 +3504,13 @@
         <v>0</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G66" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>1.484</v>
+        <v>1.504</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -3551,13 +3551,13 @@
         <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>1.629</v>
+        <v>1.619</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -3588,13 +3588,13 @@
         <v>0</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G68" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>1.504</v>
+        <v>1.524</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -3625,13 +3625,13 @@
         <v>0</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G69" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="B70" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -3699,13 +3699,13 @@
         <v>0</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G71" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         </is>
       </c>
       <c r="B72" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -3736,13 +3736,13 @@
         <v>0</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G72" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="B73" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -3773,13 +3773,13 @@
         <v>0</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G73" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="B74" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="B75" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -3847,13 +3847,13 @@
         <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G75" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="B76" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -3884,13 +3884,13 @@
         <v>0</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G76" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="B77" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3921,13 +3921,13 @@
         <v>0</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G77" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>1.609</v>
+        <v>1.599</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         </is>
       </c>
       <c r="B78" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3973,13 +3973,13 @@
         <v>0</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G78" s="3" t="n">
         <v>0.02</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>1.484</v>
+        <v>1.504</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -4025,13 +4025,13 @@
         <v>0</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G79" s="3" t="n">
         <v>0.05</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>1.639</v>
+        <v>1.629</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -4072,13 +4072,13 @@
         <v>0</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G80" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>1.504</v>
+        <v>1.524</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -4119,13 +4119,13 @@
         <v>0.04</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G81" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0.04</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G82" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="B83" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -4193,13 +4193,13 @@
         <v>0.04</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G83" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="B84" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -4230,13 +4230,13 @@
         <v>0</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G84" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="B85" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="B86" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -4304,13 +4304,13 @@
         <v>0</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G86" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="B87" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -4341,13 +4341,13 @@
         <v>0</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G87" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         </is>
       </c>
       <c r="B88" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="B89" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -4415,13 +4415,13 @@
         <v>0.04</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G89" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         </is>
       </c>
       <c r="B90" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -4452,13 +4452,13 @@
         <v>0.05</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G90" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -4489,13 +4489,13 @@
         <v>0</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G91" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>1.629</v>
+        <v>1.619</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -4526,13 +4526,13 @@
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0.04</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>1.504</v>
+        <v>1.524</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -4563,13 +4563,13 @@
         <v>0.03</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G93" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         </is>
       </c>
       <c r="B95" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -4637,13 +4637,13 @@
         <v>0.03</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G95" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N95" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         </is>
       </c>
       <c r="B96" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -4674,13 +4674,13 @@
         <v>0.04</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G96" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="B97" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="B98" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -4748,13 +4748,13 @@
         <v>0.03</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G98" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="B99" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="B100" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -4822,13 +4822,13 @@
         <v>0.03</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="B101" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -4859,13 +4859,13 @@
         <v>0.04</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G101" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="B102" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         </is>
       </c>
       <c r="B103" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -4933,13 +4933,13 @@
         <v>0.03</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G103" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N103" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         </is>
       </c>
       <c r="B104" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="B105" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -5007,13 +5007,13 @@
         <v>0.03</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G105" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N105" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="B106" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -5044,13 +5044,13 @@
         <v>0.04</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G106" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N106" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -5118,13 +5118,13 @@
         <v>0.03</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G108" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N108" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -5192,13 +5192,13 @@
         <v>0.03</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G110" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N110" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="B111" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -5229,13 +5229,13 @@
         <v>0.04</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N111" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         </is>
       </c>
       <c r="B112" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         </is>
       </c>
       <c r="B113" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -5303,13 +5303,13 @@
         <v>0.03</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G113" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N113" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         </is>
       </c>
       <c r="B114" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         </is>
       </c>
       <c r="B115" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -5377,13 +5377,13 @@
         <v>0.03</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N115" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="B116" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -5414,13 +5414,13 @@
         <v>0.04</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G116" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N116" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="B117" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="B118" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -5488,13 +5488,13 @@
         <v>0.03</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N118" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="B119" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="B120" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -5562,13 +5562,13 @@
         <v>0.03</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G120" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N120" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="B121" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -5599,13 +5599,13 @@
         <v>0.04</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G121" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N121" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="B122" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         </is>
       </c>
       <c r="B123" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -5673,13 +5673,13 @@
         <v>0.03</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G123" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N123" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         </is>
       </c>
       <c r="B124" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -5710,13 +5710,13 @@
         <v>0.03</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G124" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N124" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="B125" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         </is>
       </c>
       <c r="B126" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -5784,13 +5784,13 @@
         <v>0.04</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G126" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N126" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="B127" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         </is>
       </c>
       <c r="B128" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -5858,13 +5858,13 @@
         <v>0.03</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G128" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N128" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         </is>
       </c>
       <c r="B129" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         </is>
       </c>
       <c r="B130" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -5932,13 +5932,13 @@
         <v>0.03</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G130" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N130" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="B131" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -5969,13 +5969,13 @@
         <v>0.04</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G131" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N131" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="B132" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="B133" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -6043,13 +6043,13 @@
         <v>0.03</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G133" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N133" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         </is>
       </c>
       <c r="B134" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="B135" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0.03</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N135" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         </is>
       </c>
       <c r="B136" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -6154,13 +6154,13 @@
         <v>0.04</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G136" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N136" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="B137" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="B138" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -6228,13 +6228,13 @@
         <v>0.03</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G138" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N138" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         </is>
       </c>
       <c r="B139" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         </is>
       </c>
       <c r="B140" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -6302,13 +6302,13 @@
         <v>0.03</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G140" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N140" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         </is>
       </c>
       <c r="B141" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -6339,13 +6339,13 @@
         <v>0.04</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G141" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N141" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         </is>
       </c>
       <c r="B142" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="B143" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -6413,13 +6413,13 @@
         <v>0.03</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G143" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N143" t="inlineStr">
         <is>
@@ -6434,7 +6434,7 @@
         </is>
       </c>
       <c r="B144" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="B145" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -6487,13 +6487,13 @@
         <v>0.03</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G145" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N145" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         </is>
       </c>
       <c r="B146" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -6524,13 +6524,13 @@
         <v>0.04</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G146" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N146" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="B147" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         </is>
       </c>
       <c r="B148" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -6598,13 +6598,13 @@
         <v>0.03</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G148" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N148" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="B149" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="B150" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -6672,13 +6672,13 @@
         <v>0.03</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G150" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N150" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="B151" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -6709,13 +6709,13 @@
         <v>0.04</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G151" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N151" t="inlineStr">
         <is>
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="B152" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         </is>
       </c>
       <c r="B153" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -6783,13 +6783,13 @@
         <v>0.03</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G153" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N153" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         </is>
       </c>
       <c r="B154" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         </is>
       </c>
       <c r="B155" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -6857,13 +6857,13 @@
         <v>0.03</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G155" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N155" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="B156" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -6894,13 +6894,13 @@
         <v>0.04</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G156" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N156" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="B157" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="B158" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -6968,13 +6968,13 @@
         <v>0.03</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G158" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N158" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="B159" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="B160" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -7042,13 +7042,13 @@
         <v>0.03</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G160" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N160" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         </is>
       </c>
       <c r="B161" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -7079,13 +7079,13 @@
         <v>0.04</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G161" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N161" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="B162" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         </is>
       </c>
       <c r="B163" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -7153,13 +7153,13 @@
         <v>0.03</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G163" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N163" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         </is>
       </c>
       <c r="B164" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="B165" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -7227,13 +7227,13 @@
         <v>0.03</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G165" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N165" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         </is>
       </c>
       <c r="B166" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -7264,13 +7264,13 @@
         <v>0.04</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G166" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N166" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         </is>
       </c>
       <c r="B167" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         </is>
       </c>
       <c r="B168" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -7338,13 +7338,13 @@
         <v>0.03</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G168" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N168" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         </is>
       </c>
       <c r="B169" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         </is>
       </c>
       <c r="B170" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -7412,13 +7412,13 @@
         <v>0.03</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G170" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N170" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="B171" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -7449,13 +7449,13 @@
         <v>0.04</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G171" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N171" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="B172" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="B173" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -7523,13 +7523,13 @@
         <v>0.03</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G173" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N173" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         </is>
       </c>
       <c r="B174" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         </is>
       </c>
       <c r="B175" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -7597,13 +7597,13 @@
         <v>0.03</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G175" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N175" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="B176" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -7634,13 +7634,13 @@
         <v>0.04</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G176" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N176" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="B177" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         </is>
       </c>
       <c r="B178" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -7708,13 +7708,13 @@
         <v>0.03</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G178" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N178" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         </is>
       </c>
       <c r="B179" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         </is>
       </c>
       <c r="B180" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -7782,13 +7782,13 @@
         <v>0.03</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G180" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N180" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="B181" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -7819,13 +7819,13 @@
         <v>0.04</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G181" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N181" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         </is>
       </c>
       <c r="B182" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="B183" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -7893,13 +7893,13 @@
         <v>0.03</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G183" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N183" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         </is>
       </c>
       <c r="B184" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -7930,13 +7930,13 @@
         <v>0.03</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G184" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N184" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         </is>
       </c>
       <c r="B185" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         </is>
       </c>
       <c r="B186" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -8004,13 +8004,13 @@
         <v>0.04</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G186" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N186" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         </is>
       </c>
       <c r="B187" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         </is>
       </c>
       <c r="B188" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -8078,13 +8078,13 @@
         <v>0.03</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G188" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N188" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         </is>
       </c>
       <c r="B189" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="B190" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -8152,13 +8152,13 @@
         <v>0.03</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G190" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N190" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="B191" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -8189,13 +8189,13 @@
         <v>0.04</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G191" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N191" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         </is>
       </c>
       <c r="B192" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         </is>
       </c>
       <c r="B193" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -8263,13 +8263,13 @@
         <v>0.03</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G193" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N193" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         </is>
       </c>
       <c r="B194" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         </is>
       </c>
       <c r="B195" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -8337,13 +8337,13 @@
         <v>0.03</v>
       </c>
       <c r="F195" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G195" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N195" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         </is>
       </c>
       <c r="B196" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -8374,13 +8374,13 @@
         <v>0.04</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G196" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N196" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="B197" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         </is>
       </c>
       <c r="B198" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -8448,13 +8448,13 @@
         <v>0.03</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G198" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N198" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         </is>
       </c>
       <c r="B199" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         </is>
       </c>
       <c r="B200" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -8522,13 +8522,13 @@
         <v>0.03</v>
       </c>
       <c r="F200" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G200" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N200" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="B201" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -8559,13 +8559,13 @@
         <v>0.04</v>
       </c>
       <c r="F201" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G201" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N201" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         </is>
       </c>
       <c r="B202" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="B203" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -8633,13 +8633,13 @@
         <v>0.03</v>
       </c>
       <c r="F203" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G203" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N203" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="B204" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         </is>
       </c>
       <c r="B205" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -8707,13 +8707,13 @@
         <v>0.03</v>
       </c>
       <c r="F205" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G205" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N205" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         </is>
       </c>
       <c r="B206" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -8744,13 +8744,13 @@
         <v>0.04</v>
       </c>
       <c r="F206" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G206" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N206" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="B207" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         </is>
       </c>
       <c r="B208" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -8818,13 +8818,13 @@
         <v>0.03</v>
       </c>
       <c r="F208" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G208" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N208" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         </is>
       </c>
       <c r="B209" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         </is>
       </c>
       <c r="B210" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -8892,13 +8892,13 @@
         <v>0.03</v>
       </c>
       <c r="F210" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G210" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N210" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         </is>
       </c>
       <c r="B211" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -8929,13 +8929,13 @@
         <v>0.04</v>
       </c>
       <c r="F211" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G211" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N211" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="B212" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="B213" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -9003,13 +9003,13 @@
         <v>0.03</v>
       </c>
       <c r="F213" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G213" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N213" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         </is>
       </c>
       <c r="B214" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         </is>
       </c>
       <c r="B215" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -9077,13 +9077,13 @@
         <v>0.03</v>
       </c>
       <c r="F215" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G215" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N215" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         </is>
       </c>
       <c r="B216" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -9114,13 +9114,13 @@
         <v>0.04</v>
       </c>
       <c r="F216" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G216" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N216" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         </is>
       </c>
       <c r="B217" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="B218" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -9188,13 +9188,13 @@
         <v>0.03</v>
       </c>
       <c r="F218" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G218" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N218" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         </is>
       </c>
       <c r="B219" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="B220" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -9262,13 +9262,13 @@
         <v>0.03</v>
       </c>
       <c r="F220" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G220" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N220" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="B221" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -9299,13 +9299,13 @@
         <v>0.04</v>
       </c>
       <c r="F221" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G221" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N221" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         </is>
       </c>
       <c r="B222" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="B223" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -9373,13 +9373,13 @@
         <v>0.03</v>
       </c>
       <c r="F223" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G223" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H223" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N223" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="B224" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="B225" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -9447,13 +9447,13 @@
         <v>0.03</v>
       </c>
       <c r="F225" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G225" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H225" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N225" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         </is>
       </c>
       <c r="B226" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -9484,13 +9484,13 @@
         <v>0.04</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G226" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H226" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N226" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         </is>
       </c>
       <c r="B227" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         </is>
       </c>
       <c r="B228" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -9558,13 +9558,13 @@
         <v>0.03</v>
       </c>
       <c r="F228" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G228" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H228" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N228" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="B229" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         </is>
       </c>
       <c r="B230" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -9632,13 +9632,13 @@
         <v>0.03</v>
       </c>
       <c r="F230" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G230" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H230" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N230" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         </is>
       </c>
       <c r="B231" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -9669,13 +9669,13 @@
         <v>0.04</v>
       </c>
       <c r="F231" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G231" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H231" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N231" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         </is>
       </c>
       <c r="B232" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="B233" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -9743,13 +9743,13 @@
         <v>0.03</v>
       </c>
       <c r="F233" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G233" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H233" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N233" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         </is>
       </c>
       <c r="B234" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -9780,13 +9780,13 @@
         <v>0.03</v>
       </c>
       <c r="F234" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G234" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H234" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N234" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         </is>
       </c>
       <c r="B235" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         </is>
       </c>
       <c r="B236" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -9854,13 +9854,13 @@
         <v>0.04</v>
       </c>
       <c r="F236" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G236" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H236" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N236" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="B237" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         </is>
       </c>
       <c r="B238" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -9928,13 +9928,13 @@
         <v>0.03</v>
       </c>
       <c r="F238" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G238" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H238" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N238" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="B239" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         </is>
       </c>
       <c r="B240" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -10002,13 +10002,13 @@
         <v>0.03</v>
       </c>
       <c r="F240" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G240" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H240" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N240" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         </is>
       </c>
       <c r="B241" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -10039,13 +10039,13 @@
         <v>0.04</v>
       </c>
       <c r="F241" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G241" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H241" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N241" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         </is>
       </c>
       <c r="B242" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         </is>
       </c>
       <c r="B243" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -10113,13 +10113,13 @@
         <v>0.05</v>
       </c>
       <c r="F243" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G243" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H243" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N243" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         </is>
       </c>
       <c r="B244" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="B245" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -10187,13 +10187,13 @@
         <v>0.05</v>
       </c>
       <c r="F245" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G245" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H245" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N245" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         </is>
       </c>
       <c r="B246" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -10224,13 +10224,13 @@
         <v>0.05</v>
       </c>
       <c r="F246" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G246" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H246" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N246" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         </is>
       </c>
       <c r="B247" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -10261,13 +10261,13 @@
         <v>0.03</v>
       </c>
       <c r="F247" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G247" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H247" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N247" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         </is>
       </c>
       <c r="B248" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         </is>
       </c>
       <c r="B249" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -10335,13 +10335,13 @@
         <v>0.03</v>
       </c>
       <c r="F249" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G249" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H249" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N249" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         </is>
       </c>
       <c r="B250" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -10372,13 +10372,13 @@
         <v>0</v>
       </c>
       <c r="F250" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G250" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H250" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N250" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         </is>
       </c>
       <c r="B251" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         </is>
       </c>
       <c r="B252" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -10446,13 +10446,13 @@
         <v>0.03</v>
       </c>
       <c r="F252" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G252" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H252" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N252" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         </is>
       </c>
       <c r="B253" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         </is>
       </c>
       <c r="B254" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -10520,13 +10520,13 @@
         <v>0.03</v>
       </c>
       <c r="F254" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G254" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H254" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N254" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="B255" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -10557,13 +10557,13 @@
         <v>0</v>
       </c>
       <c r="F255" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G255" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H255" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N255" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="B256" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         </is>
       </c>
       <c r="B257" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -10631,13 +10631,13 @@
         <v>0.05</v>
       </c>
       <c r="F257" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G257" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H257" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N257" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         </is>
       </c>
       <c r="B258" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -10668,13 +10668,13 @@
         <v>0.05</v>
       </c>
       <c r="F258" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G258" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H258" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N258" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         </is>
       </c>
       <c r="B259" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -10705,13 +10705,13 @@
         <v>0.03</v>
       </c>
       <c r="F259" s="3" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="G259" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H259" s="2" t="n">
-        <v>1.589</v>
+        <v>1.579</v>
       </c>
       <c r="N259" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         </is>
       </c>
       <c r="B260" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -10742,13 +10742,13 @@
         <v>0.03</v>
       </c>
       <c r="F260" s="3" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="G260" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H260" s="2" t="n">
-        <v>1.464</v>
+        <v>1.484</v>
       </c>
       <c r="N260" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         </is>
       </c>
       <c r="B261" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         </is>
       </c>
       <c r="B262" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -10816,13 +10816,13 @@
         <v>0.04</v>
       </c>
       <c r="F262" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G262" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H262" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N262" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         </is>
       </c>
       <c r="B263" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         </is>
       </c>
       <c r="B264" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         </is>
       </c>
       <c r="B265" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -10927,13 +10927,13 @@
         <v>0.05</v>
       </c>
       <c r="F265" s="3" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="G265" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H265" s="2" t="n">
-        <v>1.71</v>
+        <v>1.728</v>
       </c>
       <c r="N265" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         </is>
       </c>
       <c r="B266" s="1" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
